--- a/sources/lei_step9.xlsx
+++ b/sources/lei_step9.xlsx
@@ -425,8 +425,8 @@
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col hidden="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
     <col hidden="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col hidden="1" min="10" max="10"/>
@@ -3609,22 +3609,27 @@
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>f,N+1 [u_d]</t>
+          <t>f,N+1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>f,N+1 [u_d]</t>
+          <t>f,N+1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Razor Rush [SNA]</t>
+          <t>Razor Rush</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Razor Rush [SNA]</t>
+          <t>Razor Rush</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>(~U)SNA; (~D)SNA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3711,22 +3716,27 @@
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>f,N+1&lt;2 [u_d]</t>
+          <t>f,N+1&lt;2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>f,N+1 &lt;2 [u_d]</t>
+          <t>f,N+1 &lt;2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Razor Rush [DGN]</t>
+          <t>Razor Rush</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Razor Rush [DGN]</t>
+          <t>Razor Rush</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>(~U)DGN; (~D)DGN</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3813,22 +3823,27 @@
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>f,N+1&lt;2&lt;1 [u_d]</t>
+          <t>f,N+1&lt;2&lt;1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>f,N+1 &lt;2 &lt;1 [u_d]</t>
+          <t>f,N+1 &lt;2 &lt;1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Razor Rush [PAN]</t>
+          <t>Razor Rush</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Razor Rush [PAN]</t>
+          <t>Razor Rush</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>(~U)PAN; (~D)PAN</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3915,22 +3930,27 @@
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>f,N+1&lt;2&lt;1&lt;2 [u_d]</t>
+          <t>f,N+1&lt;2&lt;1&lt;2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>f,N+1 &lt;2 &lt;1 &lt;2 [u_d]</t>
+          <t>f,N+1 &lt;2 &lt;1 &lt;2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Razor Rush [TGR]</t>
+          <t>Razor Rush</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Razor Rush [TGR]</t>
+          <t>Razor Rush</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>(~U)TGR; (~D)TGR</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4022,7 +4042,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>f,N+1 &lt;2 &lt;1 &lt;2 [u_d],3</t>
+          <t>f,N+1 &lt;2 &lt;1 &lt;2 ,3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4032,7 +4052,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Razor Rush [TGR] – Low Kick</t>
+          <t>Razor Rush – Low Kick</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4114,22 +4134,27 @@
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
-          <t>– &lt;4 [u_d]</t>
+          <t>– &lt;4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>f,N+1 &lt;2 &lt;1 &lt;2 [u_d] &lt;4 [u_d]</t>
+          <t>f,N+1 &lt;2 &lt;1 &lt;2 &lt;4</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>– Crane Kick [CRA]</t>
+          <t>– Crane Kick</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Razor Rush [TGR] – Crane Kick [CRA]</t>
+          <t>Razor Rush – Crane Kick</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>(~U)CRA; (~D)CRA</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4522,22 +4547,27 @@
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
-          <t>b+1 [~f]</t>
+          <t>b+1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>b+1 [~f]</t>
+          <t>b+1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Drunken Tiger Lash - [DRU]</t>
+          <t>Drunken Tiger Lash</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Drunken Tiger Lash - [DRU]</t>
+          <t>Drunken Tiger Lash</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>(~F)DRU</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4619,22 +4649,27 @@
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t>SS+1 [~f] [~d_~u]</t>
+          <t>SS+1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SS+1 [~f] [~d_~u]</t>
+          <t>SS+1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Snake Strike [TGR] [DGN]</t>
+          <t>Snake Strike</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Snake Strike [TGR] [DGN]</t>
+          <t>Snake Strike</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>(~F)TGR; (~D)DGN; (~U)DGN</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4716,22 +4751,27 @@
     <row r="53">
       <c r="B53" t="inlineStr">
         <is>
-          <t>f+1+2 [~f] [~d_~u]</t>
+          <t>f+1+2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>f+1+2 [~f] [~d_~u]</t>
+          <t>f+1+2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Twin Snake Strikes [CRA] [PAN]</t>
+          <t>Twin Snake Strikes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Twin Snake Strikes [CRA] [PAN]</t>
+          <t>Twin Snake Strikes</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>(~F)CRA; (~D)PAN; (~U)PAN</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5126,22 +5166,27 @@
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
-          <t>– &lt;4 [u_d]</t>
+          <t>– &lt;4</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>f,N+2 &lt;1 &lt;2 &lt;4 [u_d]</t>
+          <t>f,N+2 &lt;1 &lt;2 &lt;4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>– Crane Kick [CRA]</t>
+          <t>– Crane Kick</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Breaking Rush – Crane Kick [CRA]</t>
+          <t>Breaking Rush – Crane Kick</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>(~U)CRA; (~D)CRA</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5188,22 +5233,27 @@
     <row r="59">
       <c r="B59" t="inlineStr">
         <is>
-          <t>SS+2,2 [~f]</t>
+          <t>SS+2,2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SS+2 ,2 [~f]</t>
+          <t>SS+2 ,2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Drunken Rapid Fists [DRU]</t>
+          <t>Drunken Rapid Fists</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Drunken Rapid Fists [DRU]</t>
+          <t>Drunken Rapid Fists</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>(~F)DRU</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5392,27 +5442,27 @@
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>3~4 [d]</t>
+          <t>3~4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>3 ~4 [d]</t>
+          <t>3 ~4</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tornado Kick [KND]</t>
+          <t>Tornado Kick</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tornado Kick [KND]</t>
+          <t>Tornado Kick</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>BT; (~D)KND</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5499,7 +5549,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>3 ~4 [d],2</t>
+          <t>3 ~4 ,2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5509,7 +5559,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tornado Kick [KND] – Tornado Upper</t>
+          <t>Tornado Kick – Tornado Upper</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5581,27 +5631,27 @@
     <row r="63">
       <c r="B63" t="inlineStr">
         <is>
-          <t>3~4,U [d]</t>
+          <t>3~4,U</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>3 ~4,U [d]</t>
+          <t>3 ~4,U</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Triple Tornado [KND]</t>
+          <t>Triple Tornado</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Triple Tornado [KND]</t>
+          <t>Triple Tornado</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>BT; (~D)KND</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5648,27 +5698,27 @@
     <row r="64">
       <c r="B64" t="inlineStr">
         <is>
-          <t>f+3~4 [d]</t>
+          <t>f+3~4</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>f+3 ~4 [d]</t>
+          <t>f+3 ~4</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Axis Shift Tornado Kick [KND]</t>
+          <t>Axis Shift Tornado Kick</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Axis Shift Tornado Kick [KND]</t>
+          <t>Axis Shift Tornado Kick</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>BT; (~D)KND</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5755,7 +5805,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>f+3 ~4 [d],2</t>
+          <t>f+3 ~4 ,2</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5765,7 +5815,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Axis Shift Tornado Kick [KND] – Tornado Upper</t>
+          <t>Axis Shift Tornado Kick – Tornado Upper</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5837,27 +5887,27 @@
     <row r="66">
       <c r="B66" t="inlineStr">
         <is>
-          <t>f+3~4,U [d]</t>
+          <t>f+3~4,U</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>f+3 ~4,U [d]</t>
+          <t>f+3 ~4,U</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Axis Shift Tornado Kick [KND]</t>
+          <t>Axis Shift Tornado Kick</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Axis Shift Tornado Kick [KND]</t>
+          <t>Axis Shift Tornado Kick</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>BT; (~D)KND</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7202,22 +7252,27 @@
     <row r="81">
       <c r="B81" t="inlineStr">
         <is>
-          <t>–– &lt;4 [u_d]</t>
+          <t>–– &lt;4</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>f+4 ,2 ,1 &lt;2 &lt;4 [u_d]</t>
+          <t>f+4 ,2 ,1 &lt;2 &lt;4</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>–– Crane Kick [CRA]</t>
+          <t>–– Crane Kick</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Beating Kick – Rush – Crane Kick [CRA]</t>
+          <t>Beating Kick – Rush – Crane Kick</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>(~U)CRA; (~D)CRA</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7299,22 +7354,27 @@
     <row r="82">
       <c r="B82" t="inlineStr">
         <is>
-          <t>db+4 [u_d]</t>
+          <t>db+4</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>db+4 [u_d]</t>
+          <t>db+4</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rave Sweep [SNA]</t>
+          <t>Rave Sweep</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rave Sweep [SNA]</t>
+          <t>Rave Sweep</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>(~U)SNA; (~D)SNA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -7406,7 +7466,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>db+4 [u_d],4</t>
+          <t>db+4 ,4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7416,7 +7476,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rave Sweep [SNA] – Rave Spin</t>
+          <t>Rave Sweep – Rave Spin</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8375,22 +8435,27 @@
     <row r="95">
       <c r="B95" t="inlineStr">
         <is>
-          <t>– 1 [~F]</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>f+3+4 ,1 [~F]</t>
+          <t>f+3+4 ,1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>– Drunken Tiger Lash [DRU]</t>
+          <t>– Drunken Tiger Lash</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Drunken Master Parry – Drunken Tiger Lash [DRU]</t>
+          <t>Drunken Master Parry – Drunken Tiger Lash</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>(~F)DRU</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -8472,22 +8537,27 @@
     <row r="96">
       <c r="B96" t="inlineStr">
         <is>
-          <t>– 2,2 [~F]</t>
+          <t>– 2,2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>f+3+4 ,2 ,2 [~F]</t>
+          <t>f+3+4 ,2 ,2</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>– Drunken Rapid Fists [DRU]</t>
+          <t>– Drunken Rapid Fists</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Drunken Master Parry – Drunken Rapid Fists [DRU]</t>
+          <t>Drunken Master Parry – Drunken Rapid Fists</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>(~F)DRU</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10198,27 +10268,32 @@
     <row r="117">
       <c r="B117" t="inlineStr">
         <is>
-          <t>FC+4 [u_d]</t>
+          <t>FC+4</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FC+4 [u_d]</t>
+          <t>FC+4</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>d+4 [u_d]</t>
+          <t>d+4</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Rave Sweep [SNA]</t>
+          <t>Rave Sweep</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rave Sweep [SNA]</t>
+          <t>Rave Sweep</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>(~U)SNA; (~D)SNA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -10310,7 +10385,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FC+4 [u_d],4</t>
+          <t>FC+4 ,4</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10320,7 +10395,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rave Sweep [SNA] – Rave Spin</t>
+          <t>Rave Sweep – Rave Spin</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -11669,22 +11744,27 @@
     <row r="136">
       <c r="B136" t="inlineStr">
         <is>
-          <t>– 1 [u_d]</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>3 ,1 [u_d]</t>
+          <t>3 ,1</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>– Razor Rush [SNA]</t>
+          <t>– Razor Rush</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tiger Kick – Razor Rush [SNA]</t>
+          <t>Tiger Kick – Razor Rush</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>(~U)SNA; (~D)SNA</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -11751,22 +11831,27 @@
     <row r="137">
       <c r="B137" t="inlineStr">
         <is>
-          <t>– 1&lt;2 [u_d]</t>
+          <t>– 1&lt;2</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>3 ,1 &lt;2 [u_d]</t>
+          <t>3 ,1 &lt;2</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>– Razor Rush [DGN]</t>
+          <t>– Razor Rush</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tiger Kick – Razor Rush [DGN]</t>
+          <t>Tiger Kick – Razor Rush</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>(~U)DGN; (~D)DGN</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -11833,22 +11918,27 @@
     <row r="138">
       <c r="B138" t="inlineStr">
         <is>
-          <t>– 1&lt;2&lt;1 [u_d]</t>
+          <t>– 1&lt;2&lt;1</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>3 ,1 &lt;2 &lt;1 [u_d]</t>
+          <t>3 ,1 &lt;2 &lt;1</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>– Razor Rush [PAN]</t>
+          <t>– Razor Rush</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tiger Kick – Razor Rush [PAN]</t>
+          <t>Tiger Kick – Razor Rush</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>(~U)PAN; (~D)PAN</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -11915,22 +12005,27 @@
     <row r="139">
       <c r="B139" t="inlineStr">
         <is>
-          <t>– 1&lt;2&lt;1&lt;2 [u_d]</t>
+          <t>– 1&lt;2&lt;1&lt;2</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>3 ,1 &lt;2 &lt;1 &lt;2 [u_d]</t>
+          <t>3 ,1 &lt;2 &lt;1 &lt;2</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>– Razor Rush [TGR]</t>
+          <t>– Razor Rush</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tiger Kick – Razor Rush [TGR]</t>
+          <t>Tiger Kick – Razor Rush</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>(~U)TGR; (~D)TGR</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -12017,7 +12112,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>3 ,1 &lt;2 &lt;1 &lt;2 [u_d],3</t>
+          <t>3 ,1 &lt;2 &lt;1 &lt;2 ,3</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12027,7 +12122,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tiger Kick – Razor Rush [TGR] – Low Kick</t>
+          <t>Tiger Kick – Razor Rush – Low Kick</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -12109,22 +12204,27 @@
     <row r="141">
       <c r="B141" t="inlineStr">
         <is>
-          <t>–– &lt;4 [u_d]</t>
+          <t>–– &lt;4</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>3 ,1 &lt;2 &lt;1 &lt;2 [u_d] &lt;4 [u_d]</t>
+          <t>3 ,1 &lt;2 &lt;1 &lt;2 &lt;4</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>–– Crane Kick [CRA]</t>
+          <t>–– Crane Kick</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tiger Kick – Razor Rush [TGR] – Crane Kick [CRA]</t>
+          <t>Tiger Kick – Razor Rush – Crane Kick</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>(~U)CRA; (~D)CRA</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -13256,22 +13356,27 @@
     <row r="155">
       <c r="B155" t="inlineStr">
         <is>
-          <t>3 [~B]</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>3 [~B]</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Panther Tail [Art of Phoenix]</t>
+          <t>Panther Tail</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Panther Tail [Art of Phoenix]</t>
+          <t>Panther Tail</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>(~B)AOP</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -13649,22 +13754,27 @@
     <row r="159">
       <c r="B159" t="inlineStr">
         <is>
-          <t>–– &lt;4 [u_d]</t>
+          <t>–– &lt;4</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>4 ,2 ,1 &lt;2 &lt;4 [u_d]</t>
+          <t>4 ,2 ,1 &lt;2 &lt;4</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>–– Crane Kick [CRA]</t>
+          <t>–– Crane Kick</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Beating Kick – Rush – Crane Kick [CRA]</t>
+          <t>Beating Kick – Rush – Crane Kick</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>(~U)CRA; (~D)CRA</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -14025,22 +14135,27 @@
     <row r="165">
       <c r="B165" t="inlineStr">
         <is>
-          <t>1+2 [~F]</t>
+          <t>1+2</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>1+2 [~F]</t>
+          <t>1+2</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Dragon Spark - [TGR]</t>
+          <t>Dragon Spark</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Dragon Spark - [TGR]</t>
+          <t>Dragon Spark</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>(~F)TGR</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -14127,22 +14242,27 @@
     <row r="166">
       <c r="B166" t="inlineStr">
         <is>
-          <t>2 [~F]</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2 [~F]</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Dragon Roar - [TGR]</t>
+          <t>Dragon Roar</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Dragon Roar - [TGR]</t>
+          <t>Dragon Roar</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>(~F)TGR</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -14911,22 +15031,27 @@
     <row r="176">
       <c r="B176" t="inlineStr">
         <is>
-          <t>1~1~1~1~1~1 [~F]</t>
+          <t>1~1~1~1~1~1</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1 ~1 ~1 ~1 ~1 ~1 [~F]</t>
+          <t>1 ~1 ~1 ~1 ~1 ~1</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Rushing Snake [SNA]</t>
+          <t>Rushing Snake</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Rushing Snake [SNA]</t>
+          <t>Rushing Snake</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>(~F)SNA</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -15013,22 +15138,27 @@
     <row r="177">
       <c r="B177" t="inlineStr">
         <is>
-          <t>2 [~F]</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2 [~F]</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Single Snake Bite [DGN]</t>
+          <t>Single Snake Bite</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Single Snake Bite [DGN]</t>
+          <t>Single Snake Bite</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>(~F)DGN</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -15115,22 +15245,27 @@
     <row r="178">
       <c r="B178" t="inlineStr">
         <is>
-          <t>2,2 [~F]</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2 ,2 [~F]</t>
+          <t>2 ,2</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Double Snake Bite [DGN]</t>
+          <t>Double Snake Bite</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Double Snake Bite [DGN]</t>
+          <t>Double Snake Bite</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>(~F)DGN</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -15217,7 +15352,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2 ,2 [~F],4</t>
+          <t>2 ,2 ,4</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -15227,7 +15362,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Double Snake Bite [DGN] – Ankle Kick</t>
+          <t>Double Snake Bite – Ankle Kick</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -15304,7 +15439,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2 ,2 [~F],4 ,3</t>
+          <t>2 ,2 ,4 ,3</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -15314,7 +15449,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Double Snake Bite [DGN] – Ankle Drop</t>
+          <t>Double Snake Bite – Ankle Drop</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -15391,7 +15526,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2 ,2 [~F],4 ,3 ,3</t>
+          <t>2 ,2 ,4 ,3 ,3</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -15401,7 +15536,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Double Snake Bite [DGN] – Lift Up Cannon</t>
+          <t>Double Snake Bite – Lift Up Cannon</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -15483,22 +15618,27 @@
     <row r="182">
       <c r="B182" t="inlineStr">
         <is>
-          <t>2,2,2 [~F]</t>
+          <t>2,2,2</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2 ,2 ,2 [~F]</t>
+          <t>2 ,2 ,2</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Triple Snake Bite [PAN]</t>
+          <t>Triple Snake Bite</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Triple Snake Bite [PAN]</t>
+          <t>Triple Snake Bite</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>(~F)PAN</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -16484,27 +16624,27 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>b+4 [d]</t>
+          <t>b+4</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>b+4 [d]</t>
+          <t>b+4</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Tornado Kick [KND]</t>
+          <t>Tornado Kick</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tornado Kick [KND]</t>
+          <t>Tornado Kick</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>BT; (~D)KND</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -16551,27 +16691,27 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>b+4,U [d]</t>
+          <t>b+4,U</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>b+4,U [d]</t>
+          <t>b+4,U</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Triple Tornado [KND]</t>
+          <t>Triple Tornado</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Triple Tornado [KND]</t>
+          <t>Triple Tornado</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>BT; (~D)KND</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">

--- a/sources/lei_step9.xlsx
+++ b/sources/lei_step9.xlsx
@@ -1006,6 +1006,11 @@
           <t>Lei regains 10 points of energy but the throw damage is reduced to 23.</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>915f6ce4-1f16-4f29-88a0-289bf4714220</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>915f6ce4-1f16-4f29-88a0-289bf4714220</t>
@@ -1073,6 +1078,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>1fb94b7c-cb38-4d16-8f0b-b543560350e1</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>1fb94b7c-cb38-4d16-8f0b-b543560350e1</t>
@@ -1135,6 +1145,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>ffe412b1-5618-4c64-9fba-93d447318548</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>ffe412b1-5618-4c64-9fba-93d447318548</t>
@@ -1195,6 +1210,11 @@
       <c r="V11" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>3376e300-d34c-4e03-990c-8cf3dac1403a</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -16371,6 +16391,11 @@
           <t>hhlMmmhmmh</t>
         </is>
       </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>3b08195b-3ba2-4ba2-b20d-f82f3f97efcc</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>3b08195b-3ba2-4ba2-b20d-f82f3f97efcc</t>
@@ -16408,6 +16433,11 @@
           <t>hhlMmmhmLh</t>
         </is>
       </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>ad8ba5a0-00eb-4959-9a6d-1b52886c113e</t>
+        </is>
+      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>ad8ba5a0-00eb-4959-9a6d-1b52886c113e</t>
@@ -16448,6 +16478,11 @@
       <c r="Y195" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>1e9286e9-8453-4085-abd5-d467b2a34a10</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
